--- a/portfolio_semester_2.xlsx
+++ b/portfolio_semester_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\Portfolio_DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A3051E-129A-45B0-8BFC-D6F2429D3E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B057775-C095-46C0-8C40-7D55B5B133A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4FD6350A-F9E3-4323-8B0D-7580137DA570}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{4FD6350A-F9E3-4323-8B0D-7580137DA570}"/>
   </bookViews>
   <sheets>
     <sheet name="Database Systems" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="126">
   <si>
     <t>Nama</t>
   </si>
@@ -217,6 +217,207 @@
   </si>
   <si>
     <t>ZAHIR ALI IZZATURRAHMAN</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1s5NCkF5goL3_NVRBWw4OZtbQ-2rq6mU-?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1nLVlzeSUIgpGdLzJkjynncI9V12mpT71</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1KknxcMwO97mT7wr6-m7waXLrj6RMw_vC?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1I2NsmOEYaWcvpsDSwOZOQmm5-UW_SnVr?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/19iBd9d3hFGIkY5rcL-9s6z4nVqnTxMjG</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1bhQrwc4Ao_oUHABSba3Mj-wgRhK_QDHE?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1c6VKaGAt8G8H9QqGESkejzl9xOA8MnSd?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/18igXUusiff7G22mLEx2WMXTNVIm3GUQg?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1h-3Gv6h0aumtBu9p-CcDHPhQkYSV8js7?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1U2ouqL5RzXvhq1YmjcjKuO-ksKxO-NjD?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1kz_FwNM-ZExHyhLSagpCOFx7T3J1413v?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1cihLvlyhP9puE9-58Do4jTbM9qRzInPf?usp=sharing</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1xqXZ7jK6NlwrnhftrWO-5nvSrBIo9HYT?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1RrsXRy01OEAqjxghwBuFpormivFp4MhH?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1fVy55GfoX_3yVRorVHUO_orSf4gh3FXI?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1FCXyVG3MsqpSHd9LQp-OWyF0s9YBwwxw?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1d-6tYce-GOW-ARscqdnYTNDvSOLM58zx?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/10TfVyh9pr-6f9U3UzrioWsrNul4cSJBW?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1FnqmLzGh1sFOt7gd0a2vtyhDPH6WpNDv?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1HMiEq0rvxhlvp_H7ZWGZFcr9DeOwTSAy?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1hYXBMYt4SBS0KBCA48cYqw912SxEzx-9?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1fDd46QTAnD-j63Huswrq-SACAkO8snlu?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1igvN6tpTCEaH8Q6b853yC2f7uHZti6Ne?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1-ZLJA7_YLpW42u3Q6pYKdle0RKyLDK7g?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1rtFCdfyv5XYxEDY6MRiGS-DlJ4IYuAO6?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1v7EKb_ya_x1UtpYKI1VrUgScmQTlFwuU?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1zA87tf5LwPxLeugM99VQA6UcwyhuNUX1?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1I6xr6Wi79fi4NaWX_g-OBK-79kpBWD__?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1Hk1VRXMUv1DpS6Hp7imflI3dQAcUX6I-?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1CYVMKWWgn2sTiY8CNOw-HEWBbBNKT43G?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1cdMXmunk2lstEbA7uN-8Tcw9jsbaElcs?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1YpX3KUJzM1UzKzXyDnLn5VmTbMBbUHTI?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1S5auyKPhOGaLa_r_xvuZAi6sMzQ4YH-1?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1qa90e0uAGlDzDQZ66wiqJGo5bWb7jgPq?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1ayTDlgLAnGfxRIs1hs-OaxqYKxtCDYGY?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1HWJEchAWQ2NdyUIHW-dICbMG5BPupBA8?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1g3oGYP72EXlkBGW7nAp_Qh3MzP6T2gKd?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/11jTgzmMYFEQUWPpRb3CEmCE3er2sqNPq?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/194TgDISQ_TjyrpbJuxNTdrSgN8QQrS8v?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1TXdt_g0sF9AFRwqxVh0iBJhFL9lSOWN0?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1JnMd6hA8Eiq8ZONf6l4g8nmCsqYBltZZ?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1hV8BImwEObabd-It-9yc0tk_Pjuw_JX3?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1rsltxq9wmoROX17T_-si6u1XLb4j3O2g?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1cEb9kG0lsJbMNFQkVrxHucHVOj8zC_ma?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1HmvJ7i0Bp0kfhoREVYnzxFCPXEM9kkQw?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1UtMKKDqEbc1sLvBGodYTYDJ_sAfekA_f?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1zdgD02DfhWGNsDtT6-AeoqiLf-fGtiQB?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/10yjfyntAnSQ6VlaW283smm_1cwhgwdgr?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1ediu-_CDIpq408gGoJo4fZePjjCpFU07?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1nJYg_P2MNJ8fwRs9P84NjtMd5q9E74rO?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1W-ZEYPI7MD3cTKxir2HZwKM_CS1NnpRt?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1zUCL8rI9hL1fIFQURZs51K9G-UtKxXL-?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1wJiNE8kf7HHdSfO9u0LlYnBHJnT3aGGY?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1GwruyhrTt2yciPDYVQXNfDib4z7XaBzt?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1DEfwvwctwlgG_iSMzqjSZbOy5N4ecwtA?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1bcB4LHyw80sdjPKI6dlL0up7XLTF0cPQ?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1BDY2HZdoKpjuze12NY0oeiDCjSZepPNe?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1q5z1LOA2ZbhYM9F0hqyrQDGbep1IuvUw?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/18aPfdfM_cawIS6JZmsoPt-JZh-dY7lAe?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1zUefPI2wesFJqaGfSdwCxdsTjWOk4xnf?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1c-5RYd0HY3bHTNJ18ElMzm9zZVSxrL2b?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1M2lrF5-BhI62eosn8BPJq8Yvmr6tNtgr?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1wExwSjv1gp_D99x8aa6jesndjFz1Goyg?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/19-Q3J-dLW6I6FH-c1hIvnKuFqtf7TzbH?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1toTomKAPmkvF_ScOj0U369IJIJBS8Z6Y?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1zWLbBZ5rZVDZlxl2y61aWWNKC8SDhD_1?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -616,7 +817,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -630,7 +831,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -644,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -658,7 +859,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -672,7 +873,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -686,7 +887,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -700,7 +901,7 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -714,7 +915,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -728,7 +929,7 @@
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -742,7 +943,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -756,7 +957,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -770,7 +971,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -784,7 +985,7 @@
         <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -798,7 +999,7 @@
         <v>17</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -812,7 +1013,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -826,7 +1027,7 @@
         <v>19</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -836,6 +1037,12 @@
       <c r="B18" t="s">
         <v>47</v>
       </c>
+      <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
@@ -848,7 +1055,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -862,7 +1069,7 @@
         <v>21</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -876,7 +1083,7 @@
         <v>22</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -890,7 +1097,7 @@
         <v>23</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -904,7 +1111,7 @@
         <v>24</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -918,7 +1125,7 @@
         <v>25</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -932,7 +1139,7 @@
         <v>26</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -946,7 +1153,7 @@
         <v>27</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -960,7 +1167,7 @@
         <v>28</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -974,7 +1181,7 @@
         <v>29</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -988,7 +1195,7 @@
         <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1020,33 +1227,34 @@
     <hyperlink ref="C26" r:id="rId25" xr:uid="{8D8235E2-886A-472D-9CE0-5780DC4BF0AB}"/>
     <hyperlink ref="C27" r:id="rId26" xr:uid="{CB3FDDFC-CB45-473D-930C-C95AE7B3132F}"/>
     <hyperlink ref="C28" r:id="rId27" xr:uid="{D2DEB487-D28E-4E28-B8ED-190CB461C95E}"/>
-    <hyperlink ref="D2" r:id="rId28" xr:uid="{B232566D-9891-41F8-965E-68BCF5F1C227}"/>
-    <hyperlink ref="D13" r:id="rId29" xr:uid="{E5EA61B6-DEED-4799-A2F7-D9BBA4F81904}"/>
-    <hyperlink ref="D11" r:id="rId30" xr:uid="{3539244A-8232-4550-9599-E0E6B9F5A5D1}"/>
-    <hyperlink ref="D29" r:id="rId31" xr:uid="{4D224B11-17E1-4C2C-8EB5-464B6A4EBE8E}"/>
-    <hyperlink ref="D3" r:id="rId32" xr:uid="{48EB6247-1E4C-45E8-9587-43E861AB9C43}"/>
-    <hyperlink ref="D4" r:id="rId33" xr:uid="{7FE4FDC9-03DC-491D-A5B9-436DB91BD930}"/>
-    <hyperlink ref="D5" r:id="rId34" xr:uid="{DF51F868-33CA-466A-BD39-12E5C28C85D7}"/>
-    <hyperlink ref="D6" r:id="rId35" xr:uid="{62CCDFB2-CC30-45C4-830E-97F807A878AD}"/>
-    <hyperlink ref="D7" r:id="rId36" xr:uid="{938101FA-2C49-45BA-96ED-D5DDED52F6A9}"/>
-    <hyperlink ref="D8" r:id="rId37" xr:uid="{2D12C7B3-45CF-4828-BFE5-E87D256C47C7}"/>
-    <hyperlink ref="D9" r:id="rId38" xr:uid="{FD4AE8EE-77A0-4CA3-90B9-A92F380B9C0F}"/>
-    <hyperlink ref="D10" r:id="rId39" xr:uid="{13D3EA75-BE4F-468D-96DF-A1BED4B3CE01}"/>
-    <hyperlink ref="D12" r:id="rId40" xr:uid="{DACB5DE3-7113-4E2A-8E7E-A986BA5472EB}"/>
-    <hyperlink ref="D14" r:id="rId41" xr:uid="{DA89C011-2B1B-4BBC-B168-FA48D92FBB86}"/>
-    <hyperlink ref="D15" r:id="rId42" xr:uid="{BDCAF6D7-4D47-498F-AF2F-254EA4940AFA}"/>
-    <hyperlink ref="D16" r:id="rId43" xr:uid="{7704AE17-3A2F-47F0-A24F-6231E7AA1558}"/>
-    <hyperlink ref="D17" r:id="rId44" xr:uid="{356578B1-4A80-426B-8A64-AECD7FAED8CD}"/>
-    <hyperlink ref="D19" r:id="rId45" xr:uid="{AF32CE7F-97F3-411F-99AF-AD5BAB4A5420}"/>
-    <hyperlink ref="D20" r:id="rId46" xr:uid="{31C227EE-1DB9-4153-AFEF-CC63B5BA8C02}"/>
-    <hyperlink ref="D21" r:id="rId47" xr:uid="{EA44EB0C-B7BC-4F8F-A0C1-077145745B26}"/>
-    <hyperlink ref="D22" r:id="rId48" xr:uid="{EF6573B1-734E-4F43-A680-556F758051F8}"/>
-    <hyperlink ref="D23" r:id="rId49" xr:uid="{626080CA-EE60-4014-B1A5-687B430B8547}"/>
-    <hyperlink ref="D24" r:id="rId50" xr:uid="{ECFAA76F-096B-4B99-928D-2841CC0E2606}"/>
-    <hyperlink ref="D25" r:id="rId51" xr:uid="{CE16DEC0-EE5B-4E93-9956-4DF570F60AE7}"/>
-    <hyperlink ref="D26" r:id="rId52" xr:uid="{4256C999-2541-49C7-B42B-60328613AC0B}"/>
-    <hyperlink ref="D27" r:id="rId53" xr:uid="{830418FC-BAB7-4FB3-9D57-46DCFE0642BC}"/>
-    <hyperlink ref="D28" r:id="rId54" xr:uid="{79E1BD61-252F-42A4-8D3F-16C517F6E1A9}"/>
+    <hyperlink ref="D2" r:id="rId28" xr:uid="{80E28C02-5436-40E0-877A-DA6F0690EF97}"/>
+    <hyperlink ref="D6" r:id="rId29" xr:uid="{001C2D86-32CF-463E-AEC3-0E0BE40BC114}"/>
+    <hyperlink ref="D7" r:id="rId30" xr:uid="{36B84BE9-FFA8-4200-9794-4A17E01C3C35}"/>
+    <hyperlink ref="D4" r:id="rId31" xr:uid="{723EAD4D-1E4D-4E7E-8CA1-A17E8B6F6F8B}"/>
+    <hyperlink ref="D20" r:id="rId32" xr:uid="{7E0BA217-F243-43E7-922B-6AE7E7FC837F}"/>
+    <hyperlink ref="D10" r:id="rId33" xr:uid="{B4584516-7492-4800-91EB-86AD3C615379}"/>
+    <hyperlink ref="D5" r:id="rId34" xr:uid="{6AD2050C-BC21-49D3-8505-82FA8C6D9813}"/>
+    <hyperlink ref="D19" r:id="rId35" xr:uid="{7805907F-58A1-4EC9-957C-B6ACFA709AF5}"/>
+    <hyperlink ref="D28" r:id="rId36" xr:uid="{EA592A1A-FA0A-4E3B-8F46-CDD1C222D8F3}"/>
+    <hyperlink ref="D18" r:id="rId37" xr:uid="{EC48E214-01BD-4304-BBCC-4CD733EE3EF9}"/>
+    <hyperlink ref="D9" r:id="rId38" xr:uid="{CA53C1D0-0CF8-4D96-8354-0C8098998C5A}"/>
+    <hyperlink ref="D26" r:id="rId39" xr:uid="{D0BB9E0C-90A0-45A9-8EE7-F996820675A0}"/>
+    <hyperlink ref="D27" r:id="rId40" xr:uid="{8ECCD8E7-0282-4169-B5B1-1C96F8AC66D5}"/>
+    <hyperlink ref="D14" r:id="rId41" xr:uid="{7B364DDC-7BE9-4A2B-96CB-8BC6761E4734}"/>
+    <hyperlink ref="D29" r:id="rId42" xr:uid="{5BCCD0F9-85E2-4A68-A41F-B2F4DEBED7BA}"/>
+    <hyperlink ref="D11" r:id="rId43" xr:uid="{A577938C-E656-424C-9A2F-B1EB99FC95FE}"/>
+    <hyperlink ref="D17" r:id="rId44" xr:uid="{8F702B95-9EF3-498E-979E-153756570D16}"/>
+    <hyperlink ref="D8" r:id="rId45" xr:uid="{324D1858-A90B-4040-A088-9725E0353F57}"/>
+    <hyperlink ref="D25" r:id="rId46" xr:uid="{0324E0DC-5BE5-4F0A-8068-C1C3916C4CCE}"/>
+    <hyperlink ref="D12" r:id="rId47" xr:uid="{0A054A62-2550-466D-B4BA-9D5DB55BC966}"/>
+    <hyperlink ref="D3" r:id="rId48" xr:uid="{6F1E0533-81EB-4431-89C5-A90CAF09D906}"/>
+    <hyperlink ref="D24" r:id="rId49" xr:uid="{65DEE50E-F809-4CCB-9797-8FAE73EF0777}"/>
+    <hyperlink ref="D13" r:id="rId50" xr:uid="{3A2DA8FB-F8F3-408B-A8E8-AA8ECFA02A46}"/>
+    <hyperlink ref="D16" r:id="rId51" xr:uid="{610323BA-B0F7-44EB-BAA5-F69CA8D16437}"/>
+    <hyperlink ref="D21" r:id="rId52" xr:uid="{018D8076-5776-48CE-A646-C001ECFEDD85}"/>
+    <hyperlink ref="D15" r:id="rId53" xr:uid="{7177F487-B4EE-4E97-A1C8-CB9331995F72}"/>
+    <hyperlink ref="D22" r:id="rId54" xr:uid="{5E80C277-5315-4573-9957-877383458902}"/>
+    <hyperlink ref="D23" r:id="rId55" xr:uid="{51464ABF-F9B1-4FAE-9E16-67769DD039F2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1058,6 +1266,8 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="83.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -1082,10 +1292,10 @@
         <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1096,10 +1306,10 @@
         <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -1110,10 +1320,10 @@
         <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -1124,10 +1334,10 @@
         <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -1138,10 +1348,10 @@
         <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -1152,10 +1362,10 @@
         <v>36</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -1166,10 +1376,10 @@
         <v>37</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -1180,10 +1390,10 @@
         <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -1194,10 +1404,10 @@
         <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>14</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -1208,10 +1418,10 @@
         <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1222,10 +1432,10 @@
         <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -1236,10 +1446,10 @@
         <v>42</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>4</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -1250,10 +1460,10 @@
         <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -1264,10 +1474,10 @@
         <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -1278,10 +1488,10 @@
         <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -1292,10 +1502,10 @@
         <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1305,6 +1515,12 @@
       <c r="B18" t="s">
         <v>47</v>
       </c>
+      <c r="C18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
@@ -1314,10 +1530,10 @@
         <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -1328,10 +1544,10 @@
         <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1342,10 +1558,10 @@
         <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1356,10 +1572,10 @@
         <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1370,10 +1586,10 @@
         <v>52</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -1384,10 +1600,10 @@
         <v>53</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1398,10 +1614,10 @@
         <v>54</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1412,10 +1628,10 @@
         <v>55</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>27</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1426,10 +1642,10 @@
         <v>56</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -1440,10 +1656,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1454,68 +1670,16 @@
         <v>58</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{9B770602-65E6-4814-9D99-BEE567132343}"/>
-    <hyperlink ref="C13" r:id="rId2" xr:uid="{E0F836D9-6BAB-4607-B6CB-78204C5505DC}"/>
-    <hyperlink ref="C11" r:id="rId3" xr:uid="{BF866179-CE9B-4A29-BBBA-FD76AF4A7E3C}"/>
-    <hyperlink ref="C29" r:id="rId4" xr:uid="{3E8CCD41-43C8-4B76-9F31-0868E3C35AD8}"/>
-    <hyperlink ref="C3" r:id="rId5" xr:uid="{390DC81E-5CFD-40DD-A6D2-BB35222DDF0E}"/>
-    <hyperlink ref="C4" r:id="rId6" xr:uid="{8AD3A890-99CC-49B2-8F7A-178FF6CDD522}"/>
-    <hyperlink ref="C5" r:id="rId7" xr:uid="{4E83BDFD-80F9-46F2-9BA0-046F06115714}"/>
-    <hyperlink ref="C6" r:id="rId8" xr:uid="{693F62CF-CBB4-4909-890F-E53F58C7619E}"/>
-    <hyperlink ref="C7" r:id="rId9" xr:uid="{6783F506-BCC5-47F2-8A33-DEEAA00661C4}"/>
-    <hyperlink ref="C8" r:id="rId10" xr:uid="{464F4299-52F7-420D-B28F-41E48E085D39}"/>
-    <hyperlink ref="C9" r:id="rId11" xr:uid="{08340889-3D1A-44A3-A948-3575D4099A96}"/>
-    <hyperlink ref="C10" r:id="rId12" xr:uid="{0463B3C4-DB26-4482-AF9A-E49CED280159}"/>
-    <hyperlink ref="C12" r:id="rId13" xr:uid="{E9926E7F-08B3-4B1F-AE5D-AE48C0B6DDB0}"/>
-    <hyperlink ref="C14" r:id="rId14" xr:uid="{23CB2F3A-F133-4308-B778-B7CE1891DFD2}"/>
-    <hyperlink ref="C15" r:id="rId15" xr:uid="{FCDEEDA2-C06B-4E4F-9D2B-C1F32552EC27}"/>
-    <hyperlink ref="C16" r:id="rId16" xr:uid="{D4AACDB3-B823-40E7-9233-457D6AE49935}"/>
-    <hyperlink ref="C17" r:id="rId17" xr:uid="{3B54F5B1-BD6E-47DD-A59D-36962F781BEB}"/>
-    <hyperlink ref="C19" r:id="rId18" xr:uid="{641C2EEB-7712-450A-896A-49794DC088E5}"/>
-    <hyperlink ref="C20" r:id="rId19" xr:uid="{34E63D42-8910-46EA-B6C4-B6EEFFC7779C}"/>
-    <hyperlink ref="C21" r:id="rId20" xr:uid="{E6177A50-24B8-4EF9-B3F7-321235094DFB}"/>
-    <hyperlink ref="C22" r:id="rId21" xr:uid="{E64E0060-3F18-48C8-9E0B-1772DF28516A}"/>
-    <hyperlink ref="C23" r:id="rId22" xr:uid="{49A48AB8-97FE-41BD-BE0C-593212EA2511}"/>
-    <hyperlink ref="C24" r:id="rId23" xr:uid="{3624EFAA-2D63-4190-86EC-9EEACC96B143}"/>
-    <hyperlink ref="C25" r:id="rId24" xr:uid="{0564378B-236E-46FF-8BEA-A26E804ABAE7}"/>
-    <hyperlink ref="C26" r:id="rId25" xr:uid="{69DD0900-AB0D-4127-B709-5860C78A4F41}"/>
-    <hyperlink ref="C27" r:id="rId26" xr:uid="{487E2622-56D2-4BA2-8092-3B7C55171E95}"/>
-    <hyperlink ref="C28" r:id="rId27" xr:uid="{6003A9D3-ED5C-4674-84EE-761B5E75FF5B}"/>
-    <hyperlink ref="D2" r:id="rId28" xr:uid="{970A3F37-9F7D-43BF-8BB4-8880F4E2F93D}"/>
-    <hyperlink ref="D13" r:id="rId29" xr:uid="{DD8B6A84-26AD-4DDE-AA2F-5307673145A9}"/>
-    <hyperlink ref="D11" r:id="rId30" xr:uid="{A6D51BB8-2A16-4B64-9449-88C687F1A58C}"/>
-    <hyperlink ref="D29" r:id="rId31" xr:uid="{33DD24A4-05F8-4C5F-86A8-1EE146CFAB2A}"/>
-    <hyperlink ref="D3" r:id="rId32" xr:uid="{7D752F3E-7DB7-4ECA-987A-DFC090F926A0}"/>
-    <hyperlink ref="D4" r:id="rId33" xr:uid="{1FEE3E6F-E36B-4F71-BC2A-F1C0423DF371}"/>
-    <hyperlink ref="D5" r:id="rId34" xr:uid="{DBDAD456-F172-4982-A19D-626FC202DCD3}"/>
-    <hyperlink ref="D6" r:id="rId35" xr:uid="{79A34278-0A6F-4FCB-9312-86A55A292475}"/>
-    <hyperlink ref="D7" r:id="rId36" xr:uid="{D5676B14-56FB-41B9-8E95-C8759C8157E0}"/>
-    <hyperlink ref="D8" r:id="rId37" xr:uid="{8CF754DD-A640-4E08-B6F6-581094B5CD85}"/>
-    <hyperlink ref="D9" r:id="rId38" xr:uid="{C5A221EA-CF07-422F-9844-546238E45A77}"/>
-    <hyperlink ref="D10" r:id="rId39" xr:uid="{8D965132-41C3-4257-9679-93F46E7CE828}"/>
-    <hyperlink ref="D12" r:id="rId40" xr:uid="{610C8AAB-00B4-42D2-AA6B-EB0AADC4D237}"/>
-    <hyperlink ref="D14" r:id="rId41" xr:uid="{EF604650-36B2-48C9-A07C-6CA7C1D4C102}"/>
-    <hyperlink ref="D15" r:id="rId42" xr:uid="{DB123DC5-1732-423D-8F1C-748A943DBA2C}"/>
-    <hyperlink ref="D16" r:id="rId43" xr:uid="{01692D0B-FD65-433B-9A46-54EF1AF4FA07}"/>
-    <hyperlink ref="D17" r:id="rId44" xr:uid="{9AF13FD7-7139-4CD4-938F-C39E8042CD7E}"/>
-    <hyperlink ref="D19" r:id="rId45" xr:uid="{6FA6764E-434A-41AF-BB66-B90A53FAA0B1}"/>
-    <hyperlink ref="D20" r:id="rId46" xr:uid="{1A5FC499-35F3-475B-A3AA-2AEB45C2D52E}"/>
-    <hyperlink ref="D21" r:id="rId47" xr:uid="{2F6FCFC3-2C7F-48FB-8535-5095678FFEBB}"/>
-    <hyperlink ref="D22" r:id="rId48" xr:uid="{413900D1-904A-4D07-81BB-D28E30B2296A}"/>
-    <hyperlink ref="D23" r:id="rId49" xr:uid="{30B0085A-7AAB-4814-B0AD-256008CC8A49}"/>
-    <hyperlink ref="D24" r:id="rId50" xr:uid="{021A00AD-177A-4D83-AF6D-77D4E38D9DBE}"/>
-    <hyperlink ref="D25" r:id="rId51" xr:uid="{5E7C7F9A-DB60-4EC3-ADF6-7D6E252D040A}"/>
-    <hyperlink ref="D26" r:id="rId52" xr:uid="{0AD38337-3205-41A8-9090-F812875C689D}"/>
-    <hyperlink ref="D27" r:id="rId53" xr:uid="{1F1CD8A6-8837-43B5-A69C-ADD57A865850}"/>
-    <hyperlink ref="D28" r:id="rId54" xr:uid="{2856A2A9-6364-4071-A1E6-41D99D532716}"/>
+    <hyperlink ref="C18" r:id="rId1" xr:uid="{B8CAA84B-8C44-4BB5-B22D-CFCFDE18EAB0}"/>
+    <hyperlink ref="D18" r:id="rId2" xr:uid="{F6460091-EED8-4977-B62A-023590036AFE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
